--- a/test_bom.xlsx
+++ b/test_bom.xlsx
@@ -1,26 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1826ACD-3616-454C-85FE-21E2813274CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="test için bir excel oluşştur" sheetId="1" r:id="rId1"/>
+    <sheet name="test için bir excel oluşştur" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>RefDes</t>
   </si>
@@ -37,7 +33,7 @@
     <t>Qty</t>
   </si>
   <si>
-    <t>R1, R2</t>
+    <t>R1</t>
   </si>
   <si>
     <t>RC0402JR-0710KL</t>
@@ -46,22 +42,10 @@
     <t>Yageo</t>
   </si>
   <si>
-    <t>RES SMD 10K OHM %5 1/16W 0402</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>CRCW060310K0FKEA</t>
-  </si>
-  <si>
-    <t>Vishay</t>
-  </si>
-  <si>
-    <t>RES SMD 10K OHM %1 1/10W 0603</t>
-  </si>
-  <si>
-    <t>C1, C2</t>
+    <t xml:space="preserve">RES SMD 10K OHM %5 1/16W 0402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1, C2</t>
   </si>
   <si>
     <t>CL10A106KP8NNNC</t>
@@ -70,58 +54,19 @@
     <t>Samsung</t>
   </si>
   <si>
-    <t>CAP CER 10UF 10V X5R 0603</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>STM32F405RGT6</t>
-  </si>
-  <si>
-    <t>STMicroelectronics</t>
-  </si>
-  <si>
-    <t>IC MCU 32BIT 1MB FLASH 64LQFP</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>MAX232CSE+</t>
-  </si>
-  <si>
-    <t>Maxim Integrated</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>BC817-25,215</t>
-  </si>
-  <si>
-    <t>Nexperia</t>
-  </si>
-  <si>
-    <t>TRANS NPN 45V 0.8A SOT23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IC TXRX RS232 16SOIC </t>
+    <t xml:space="preserve">CAP CER 10UF 10V X5R 0603</t>
+  </si>
+  <si>
+    <t>R2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1">
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="10.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -137,19 +82,20 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="3">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -167,8 +113,291 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -225,7 +454,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -251,7 +480,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -328,7 +557,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -359,19 +588,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -388,8 +616,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -402,10 +630,10 @@
         <v>8</v>
       </c>
       <c r="E2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -419,78 +647,51 @@
         <v>12</v>
       </c>
       <c r="E3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="1">
-        <v>2</v>
-      </c>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
+    <row r="6">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
+    <row r="7">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>